--- a/output/customer_segmentation_output.xlsx
+++ b/output/customer_segmentation_output.xlsx
@@ -532,11 +532,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>200001</v>
+        <v>200034</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mia Wilson</t>
+          <t>Harry Jones</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -551,20 +551,20 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3348</v>
+        <v>18199</v>
       </c>
       <c r="K2" t="n">
-        <v>152</v>
+        <v>21</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.19</v>
+        <v>0.59</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -601,26 +601,26 @@
         <v>10</v>
       </c>
       <c r="R2" t="n">
-        <v>40</v>
+        <v>120</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>200002</v>
+        <v>200053</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mia Thompson</t>
+          <t>Oscar White</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -635,46 +635,46 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>26905</v>
+        <v>24569</v>
       </c>
       <c r="K3" t="n">
-        <v>41</v>
+        <v>83</v>
       </c>
       <c r="L3" t="n">
         <v>1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="O3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -685,26 +685,26 @@
         <v>8</v>
       </c>
       <c r="R3" t="n">
-        <v>10</v>
+        <v>115</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>200003</v>
+        <v>200027</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grace Evans</t>
+          <t>Thomas Evans</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Digital Natives</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>236</v>
+        <v>56</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -741,13 +741,13 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>12903</v>
+        <v>26269</v>
       </c>
       <c r="K4" t="n">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -755,40 +755,40 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.53</v>
+        <v>0.1</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R4" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>CTF to ISA conversion call</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>200004</v>
+        <v>200064</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sophia Jones</t>
+          <t>Aarav Patel</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -798,21 +798,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>East Midlands</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>27832</v>
+        <v>5270</v>
       </c>
       <c r="K5" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -839,64 +839,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0.57</v>
+        <v>0.67</v>
       </c>
       <c r="O5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R5" t="n">
-        <v>65</v>
+        <v>105</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>200005</v>
+        <v>200056</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Evie Wilson</t>
+          <t>Evie Thompson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>237</v>
+        <v>28</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>21471</v>
+        <v>25287</v>
       </c>
       <c r="K6" t="n">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0.72</v>
+        <v>0.17</v>
       </c>
       <c r="O6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -934,39 +934,39 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R6" t="n">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Over 50 retention call</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>200006</v>
+        <v>200013</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oscar Jones</t>
+          <t>Mia Jones</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -976,15 +976,15 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>291</v>
+        <v>170</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -993,59 +993,59 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>21977</v>
+        <v>22421</v>
       </c>
       <c r="K7" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0.39</v>
+        <v>0.8</v>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="R7" t="n">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>CTF to ISA conversion call</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>200007</v>
+        <v>200031</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Thomas Wright</t>
+          <t>Mia Davies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1055,16 +1055,16 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>205</v>
+        <v>13</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1077,13 +1077,13 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5032</v>
+        <v>20530</v>
       </c>
       <c r="K8" t="n">
-        <v>131</v>
+        <v>218</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1091,40 +1091,40 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q8" t="n">
         <v>10</v>
       </c>
       <c r="R8" t="n">
-        <v>20</v>
+        <v>105</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>CTF to ISA conversion call</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>200008</v>
+        <v>200023</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Jack Walker</t>
+          <t>Amelia Jones</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1134,21 +1134,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Comfortable Families</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>240</v>
+        <v>280</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>28706</v>
+        <v>18605</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="O9" t="n">
         <v>12</v>
@@ -1186,29 +1186,29 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="R9" t="n">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>High Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>200009</v>
+        <v>200084</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Freya Brown</t>
+          <t>Isla Patel</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1228,15 +1228,15 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1245,24 +1245,24 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>9130</v>
+        <v>20392</v>
       </c>
       <c r="K10" t="n">
-        <v>129</v>
+        <v>114</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="O10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1270,29 +1270,29 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R10" t="n">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>200010</v>
+        <v>200008</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Muhammad Roberts</t>
+          <t>Jack Walker</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Comfortable Families</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>277</v>
+        <v>240</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>518</v>
+        <v>28706</v>
       </c>
       <c r="K11" t="n">
-        <v>154</v>
+        <v>3</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="O11" t="n">
         <v>12</v>
@@ -1354,69 +1354,69 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="R11" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>200011</v>
+        <v>200066</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Noah White</t>
+          <t>Freya Evans</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Comfortable Families</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>273</v>
+        <v>155</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>16074</v>
+        <v>16333</v>
       </c>
       <c r="K12" t="n">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1438,29 +1438,29 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>200012</v>
+        <v>200021</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sophia Walker</t>
+          <t>Evie Thomas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1480,15 +1480,15 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>East Midlands</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>225</v>
+        <v>69</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1497,24 +1497,24 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8623</v>
+        <v>24827</v>
       </c>
       <c r="K13" t="n">
-        <v>58</v>
+        <v>142</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0.47</v>
+        <v>0.18</v>
       </c>
       <c r="O13" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1522,53 +1522,53 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="R13" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>200013</v>
+        <v>200030</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mia Jones</t>
+          <t>Harry Thompson</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Digital Natives</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>South East</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>170</v>
+        <v>346</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1581,10 +1581,10 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>22421</v>
+        <v>26584</v>
       </c>
       <c r="K14" t="n">
-        <v>125</v>
+        <v>189</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -1595,10 +1595,10 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0.8</v>
+        <v>0.44</v>
       </c>
       <c r="O14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1606,53 +1606,53 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R14" t="n">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>JISA maturity follow-up</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>200014</v>
+        <v>200004</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>George Williams</t>
+          <t>Sophia Jones</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>338</v>
+        <v>52</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>15803</v>
+        <v>27832</v>
       </c>
       <c r="K15" t="n">
-        <v>222</v>
+        <v>94</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>0.84</v>
+        <v>0.57</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>200015</v>
+        <v>200018</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>George Davies</t>
+          <t>Charlie Jones</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Yorkshire</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>230</v>
+        <v>36</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1749,24 +1749,24 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>15659</v>
+        <v>8207</v>
       </c>
       <c r="K16" t="n">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="O16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1774,29 +1774,29 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="R16" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Over 50 retention call</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>200016</v>
+        <v>200081</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noah Wilson</t>
+          <t>Olivia Thomas</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1806,21 +1806,21 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1833,24 +1833,24 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13641</v>
+        <v>7471</v>
       </c>
       <c r="K17" t="n">
-        <v>232</v>
+        <v>40</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N17" t="n">
-        <v>0.84</v>
+        <v>0.09</v>
       </c>
       <c r="O17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1858,29 +1858,29 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>35</v>
+        <v>90</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>200017</v>
+        <v>200050</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Evie White</t>
+          <t>Thomas Wright</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1890,21 +1890,21 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>98</v>
+        <v>292</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1917,59 +1917,59 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>19478</v>
+        <v>24751</v>
       </c>
       <c r="K18" t="n">
-        <v>189</v>
+        <v>26</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N18" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="O18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R18" t="n">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Very High Priority</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>200018</v>
+        <v>200049</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Charlie Jones</t>
+          <t>Muhammad Taylor</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1979,16 +1979,16 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>36</v>
+        <v>156</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8207</v>
+        <v>18786</v>
       </c>
       <c r="K19" t="n">
-        <v>104</v>
+        <v>196</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -2015,40 +2015,40 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>0.21</v>
+        <v>0.53</v>
       </c>
       <c r="O19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q19" t="n">
         <v>15</v>
       </c>
       <c r="R19" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>200019</v>
+        <v>200045</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Oscar Davies</t>
+          <t>Jack Wilson</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2058,21 +2058,21 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Digital Natives</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>East Midlands</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>123</v>
+        <v>340</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2081,14 +2081,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>21651</v>
+        <v>17897</v>
       </c>
       <c r="K20" t="n">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2099,10 +2099,10 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2110,53 +2110,53 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>CTF to ISA conversion call</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>200020</v>
+        <v>200060</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Evie Davies</t>
+          <t>Leo Davies</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Comfortable Families</t>
+          <t>Mass Market Mainstream</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Yorkshire</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>136</v>
+        <v>293</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2754</v>
+        <v>13960</v>
       </c>
       <c r="K21" t="n">
-        <v>226</v>
+        <v>12</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -2183,10 +2183,10 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>0.37</v>
+        <v>0.78</v>
       </c>
       <c r="O21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2194,39 +2194,39 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>200021</v>
+        <v>200070</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Evie Thomas</t>
+          <t>Jack Smith</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Comfortable Families</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2236,11 +2236,11 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>69</v>
+        <v>275</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>24827</v>
+        <v>25043</v>
       </c>
       <c r="K22" t="n">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2267,64 +2267,64 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>0.18</v>
+        <v>0.54</v>
       </c>
       <c r="O22" t="n">
         <v>5</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="R22" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Over 50 retention call</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>200022</v>
+        <v>200076</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Oscar Patel</t>
+          <t>Aarav Brown</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mass Market Mainstream</t>
+          <t>Digital Natives</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>325</v>
+        <v>27</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2337,13 +2337,13 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>616</v>
+        <v>4224</v>
       </c>
       <c r="K23" t="n">
-        <v>86</v>
+        <v>191</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2351,68 +2351,68 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
       <c r="O23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R23" t="n">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>JISA maturity follow-up</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>200023</v>
+        <v>200059</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Amelia Jones</t>
+          <t>Charlie Evans</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Digital Natives</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>280</v>
+        <v>145</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2421,10 +2421,10 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>18605</v>
+        <v>19502</v>
       </c>
       <c r="K24" t="n">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>0.31</v>
+        <v>0.46</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -2446,57 +2446,57 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R24" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>JISA maturity follow-up</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>200024</v>
+        <v>200097</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Mia Williams</t>
+          <t>Ella Thomas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Mass Market Mainstream</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>East Midlands</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>287</v>
+        <v>120</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>20837</v>
+        <v>26996</v>
       </c>
       <c r="K25" t="n">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>0.73</v>
+        <v>0.31</v>
       </c>
       <c r="O25" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2530,53 +2530,53 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>25</v>
+        <v>85</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>200025</v>
+        <v>200015</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Leo Wright</t>
+          <t>George Davies</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>Yorkshire</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>137</v>
+        <v>230</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2589,78 +2589,78 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>13035</v>
+        <v>15659</v>
       </c>
       <c r="K26" t="n">
-        <v>224</v>
+        <v>64</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>0.17</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>200026</v>
+        <v>200017</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aarav Davies</t>
+          <t>Evie White</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>169</v>
+        <v>98</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2669,14 +2669,14 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>25840</v>
+        <v>19478</v>
       </c>
       <c r="K27" t="n">
-        <v>72</v>
+        <v>189</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2687,45 +2687,45 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0.58</v>
+        <v>0.05</v>
       </c>
       <c r="O27" t="n">
+        <v>9</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>5</v>
-      </c>
       <c r="R27" t="n">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>200027</v>
+        <v>200025</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Thomas Evans</t>
+          <t>Leo Wright</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2735,16 +2735,16 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>South East</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>26269</v>
+        <v>13035</v>
       </c>
       <c r="K28" t="n">
-        <v>81</v>
+        <v>224</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2771,64 +2771,64 @@
         </is>
       </c>
       <c r="N28" t="n">
-        <v>0.1</v>
+        <v>0.17</v>
       </c>
       <c r="O28" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q28" t="n">
         <v>14</v>
       </c>
       <c r="R28" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>Over 50 retention call</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>200028</v>
+        <v>200026</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Charlie Davies</t>
+          <t>Aarav Davies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>East Midlands</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>221</v>
+        <v>169</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2837,14 +2837,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>11319</v>
+        <v>25840</v>
       </c>
       <c r="K29" t="n">
-        <v>160</v>
+        <v>72</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2855,10 +2855,10 @@
         </is>
       </c>
       <c r="N29" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -2866,57 +2866,57 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R29" t="n">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>Over 50 retention call</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>200029</v>
+        <v>200047</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Sophia Taylor</t>
+          <t>Sophia Wilson</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>East Midlands</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>216</v>
+        <v>92</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2925,24 +2925,24 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>25014</v>
+        <v>4647</v>
       </c>
       <c r="K30" t="n">
-        <v>232</v>
+        <v>71</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N30" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -2950,39 +2950,39 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>JISA maturity follow-up</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>200030</v>
+        <v>200090</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Harry Thompson</t>
+          <t>Thomas Johnson</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Digital Natives</t>
+          <t>Mass Market Mainstream</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2992,11 +2992,11 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>East Midlands</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3009,24 +3009,24 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>26584</v>
+        <v>21189</v>
       </c>
       <c r="K31" t="n">
-        <v>189</v>
+        <v>78</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N31" t="n">
-        <v>0.44</v>
+        <v>0.3</v>
       </c>
       <c r="O31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -3034,57 +3034,57 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R31" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>200031</v>
+        <v>200032</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mia Davies</t>
+          <t>Mia Taylor</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3093,35 +3093,35 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>20530</v>
+        <v>26849</v>
       </c>
       <c r="K32" t="n">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N32" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N32" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O32" t="n">
-        <v>9</v>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R32" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -3130,22 +3130,22 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>200032</v>
+        <v>200036</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mia Taylor</t>
+          <t>Evie Wilson</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3160,15 +3160,15 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>South East</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>55</v>
+        <v>113</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3177,24 +3177,24 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>26849</v>
+        <v>13242</v>
       </c>
       <c r="K33" t="n">
-        <v>179</v>
+        <v>87</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0.21</v>
+        <v>0.62</v>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -3205,31 +3205,31 @@
         <v>8</v>
       </c>
       <c r="R33" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>JISA maturity follow-up</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>200033</v>
+        <v>200085</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ella Wright</t>
+          <t>Charlie Thomas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3244,15 +3244,15 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Yorkshire</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>229</v>
+        <v>113</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="J34" t="n">
-        <v>16054</v>
+        <v>751</v>
       </c>
       <c r="K34" t="n">
-        <v>116</v>
+        <v>53</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0.54</v>
+        <v>0.12</v>
       </c>
       <c r="O34" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -3289,50 +3289,50 @@
         <v>7</v>
       </c>
       <c r="R34" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>JISA maturity follow-up</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>200034</v>
+        <v>200039</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Harry Jones</t>
+          <t>Mia Taylor</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>121</v>
+        <v>343</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>18199</v>
+        <v>15738</v>
       </c>
       <c r="K35" t="n">
-        <v>21</v>
+        <v>180</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0.59</v>
+        <v>0.52</v>
       </c>
       <c r="O35" t="n">
         <v>11</v>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R35" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="S35" t="inlineStr">
         <is>
@@ -3382,17 +3382,17 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>CTF to ISA conversion call</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>200035</v>
+        <v>200080</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Freya Patel</t>
+          <t>Noah Jones</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3402,21 +3402,21 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Mass Market Mainstream</t>
+          <t>Comfortable Families</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3429,13 +3429,13 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>23290</v>
+        <v>27100</v>
       </c>
       <c r="K36" t="n">
-        <v>6</v>
+        <v>34</v>
       </c>
       <c r="L36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0.32</v>
+        <v>0.48</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -3454,29 +3454,29 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R36" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>200036</v>
+        <v>200044</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Evie Wilson</t>
+          <t>Evie Smith</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3486,21 +3486,21 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>Yorkshire</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3513,10 +3513,10 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>13242</v>
+        <v>16509</v>
       </c>
       <c r="K37" t="n">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0.62</v>
+        <v>0.55</v>
       </c>
       <c r="O37" t="n">
         <v>7</v>
@@ -3538,39 +3538,39 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R37" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>JISA maturity follow-up</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>200037</v>
+        <v>200005</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Thomas Smith</t>
+          <t>Evie Wilson</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3580,11 +3580,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>330</v>
+        <v>237</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3597,13 +3597,13 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>6454</v>
+        <v>21471</v>
       </c>
       <c r="K38" t="n">
-        <v>13</v>
+        <v>177</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -3611,64 +3611,64 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0.39</v>
+        <v>0.72</v>
       </c>
       <c r="O38" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="R38" t="n">
-        <v>35</v>
+        <v>75</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>200038</v>
+        <v>200055</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Noah White</t>
+          <t>Isla Johnson</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Comfortable Families</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>South East</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>277</v>
+        <v>356</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3681,24 +3681,24 @@
         </is>
       </c>
       <c r="J39" t="n">
-        <v>7847</v>
+        <v>13622</v>
       </c>
       <c r="K39" t="n">
-        <v>167</v>
+        <v>209</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -3706,29 +3706,29 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R39" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>200039</v>
+        <v>200003</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mia Taylor</t>
+          <t>Grace Evans</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Digital Natives</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3748,11 +3748,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>343</v>
+        <v>236</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3765,13 +3765,13 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>15738</v>
+        <v>12903</v>
       </c>
       <c r="K40" t="n">
-        <v>180</v>
+        <v>21</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -3779,10 +3779,10 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="O40" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -3790,57 +3790,57 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R40" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>CTF to ISA conversion call</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>200040</v>
+        <v>200037</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Amelia Smith</t>
+          <t>Thomas Smith</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>295</v>
+        <v>330</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>13497</v>
+        <v>6454</v>
       </c>
       <c r="K41" t="n">
-        <v>184</v>
+        <v>13</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -3863,40 +3863,40 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>0.71</v>
+        <v>0.39</v>
       </c>
       <c r="O41" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R41" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Over 50 retention call</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>200041</v>
+        <v>200088</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Thomas Patel</t>
+          <t>Freya Williams</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3911,16 +3911,16 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>East Midlands</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3933,10 +3933,10 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>17079</v>
+        <v>13468</v>
       </c>
       <c r="K42" t="n">
-        <v>166</v>
+        <v>223</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -3947,55 +3947,55 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
       <c r="O42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q42" t="n">
         <v>12</v>
       </c>
       <c r="R42" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>200042</v>
+        <v>200033</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Freya Brown</t>
+          <t>Ella Wright</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Mass Market Mainstream</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4004,11 +4004,11 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>334</v>
+        <v>229</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4017,24 +4017,24 @@
         </is>
       </c>
       <c r="J43" t="n">
-        <v>18134</v>
+        <v>16054</v>
       </c>
       <c r="K43" t="n">
-        <v>199</v>
+        <v>116</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0.62</v>
+        <v>0.54</v>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -4042,29 +4042,29 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R43" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>Over 50 retention call</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>200043</v>
+        <v>200095</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Harry Wilson</t>
+          <t>Charlie Jones</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4074,21 +4074,21 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -4101,82 +4101,82 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>1440</v>
+        <v>6406</v>
       </c>
       <c r="K44" t="n">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="O44" t="n">
         <v>2</v>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N44" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="O44" t="n">
-        <v>12</v>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R44" t="n">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>JISA maturity follow-up</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>200044</v>
+        <v>200083</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Evie Smith</t>
+          <t>Noah Taylor</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Yorkshire</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4185,13 +4185,13 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>16509</v>
+        <v>14257</v>
       </c>
       <c r="K45" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="N45" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -4210,53 +4210,53 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R45" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>CTF to ISA conversion call</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>200045</v>
+        <v>200042</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Jack Wilson</t>
+          <t>Freya Brown</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>Yorkshire</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -4269,10 +4269,10 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>17897</v>
+        <v>18134</v>
       </c>
       <c r="K46" t="n">
-        <v>89</v>
+        <v>199</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>0.28</v>
+        <v>0.62</v>
       </c>
       <c r="O46" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -4294,57 +4294,57 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R46" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>JISA maturity follow-up</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>200046</v>
+        <v>200089</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>George Johnson</t>
+          <t>Grace Roberts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Comfortable Families</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>275</v>
+        <v>121</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4353,13 +4353,13 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>6776</v>
+        <v>6185</v>
       </c>
       <c r="K47" t="n">
-        <v>56</v>
+        <v>155</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0.5</v>
+        <v>0.06</v>
       </c>
       <c r="O47" t="n">
         <v>12</v>
@@ -4378,53 +4378,53 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>200047</v>
+        <v>200092</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sophia Wilson</t>
+          <t>Charlie Taylor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Mass Market Mainstream</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>East Midlands</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>92</v>
+        <v>231</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4437,24 +4437,24 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>4647</v>
+        <v>11753</v>
       </c>
       <c r="K48" t="n">
-        <v>71</v>
+        <v>183</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N48" t="n">
-        <v>0.25</v>
+        <v>0.03</v>
       </c>
       <c r="O48" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -4462,29 +4462,29 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R48" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>CTF to ISA conversion call</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>200048</v>
+        <v>200079</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Thomas Thomas</t>
+          <t>Freya Thompson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -4504,11 +4504,11 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>246</v>
+        <v>212</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4521,13 +4521,13 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>2183</v>
+        <v>14131</v>
       </c>
       <c r="K49" t="n">
-        <v>65</v>
+        <v>187</v>
       </c>
       <c r="L49" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -4535,10 +4535,10 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
       <c r="O49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -4546,29 +4546,29 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>200049</v>
+        <v>200065</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Muhammad Taylor</t>
+          <t>Emily Taylor</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4578,21 +4578,21 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>156</v>
+        <v>237</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4605,13 +4605,13 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>18786</v>
+        <v>22351</v>
       </c>
       <c r="K50" t="n">
-        <v>196</v>
+        <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -4619,64 +4619,64 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="O50" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R50" t="n">
-        <v>45</v>
+        <v>70</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>200050</v>
+        <v>200094</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Thomas Wright</t>
+          <t>Leo Jones</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4689,13 +4689,13 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>24751</v>
+        <v>21997</v>
       </c>
       <c r="K51" t="n">
-        <v>26</v>
+        <v>179</v>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -4703,64 +4703,64 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0.18</v>
+        <v>0.6</v>
       </c>
       <c r="O51" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R51" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>JISA maturity follow-up</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>200051</v>
+        <v>200012</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Isla Smith</t>
+          <t>Sophia Walker</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Comfortable Families</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>East Midlands</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -4773,24 +4773,24 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>1569</v>
+        <v>8623</v>
       </c>
       <c r="K52" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0.73</v>
+        <v>0.47</v>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -4798,39 +4798,39 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>High Priority</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>ISA reinvestment call</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>200052</v>
+        <v>200093</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Amelia Wilson</t>
+          <t>Grace Roberts</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4840,30 +4840,30 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J53" t="n">
-        <v>5936</v>
+        <v>20091</v>
       </c>
       <c r="K53" t="n">
-        <v>203</v>
+        <v>14</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -4871,10 +4871,10 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0.48</v>
+        <v>0.06</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -4882,29 +4882,29 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="R53" t="n">
-        <v>-15</v>
+        <v>65</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>200053</v>
+        <v>200075</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Oscar White</t>
+          <t>Mia Johnson</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4914,21 +4914,21 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>42</v>
+        <v>306</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -4941,64 +4941,64 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>24569</v>
+        <v>5241</v>
       </c>
       <c r="K54" t="n">
-        <v>83</v>
+        <v>34</v>
       </c>
       <c r="L54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="O54" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>High Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>200054</v>
+        <v>200071</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Thomas Patel</t>
+          <t>Ella Wilson</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Digital Natives</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5008,15 +5008,15 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>241</v>
+        <v>326</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5025,54 +5025,54 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>9614</v>
+        <v>10402</v>
       </c>
       <c r="K55" t="n">
-        <v>47</v>
+        <v>167</v>
       </c>
       <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O55" t="n">
         <v>4</v>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N55" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="O55" t="n">
-        <v>1</v>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>200055</v>
+        <v>200001</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Isla Johnson</t>
+          <t>Mia Wilson</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -5082,25 +5082,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Comfortable Families</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>356</v>
+        <v>53</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5109,13 +5109,13 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>13622</v>
+        <v>3348</v>
       </c>
       <c r="K56" t="n">
-        <v>209</v>
+        <v>152</v>
       </c>
       <c r="L56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -5123,10 +5123,10 @@
         </is>
       </c>
       <c r="N56" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="O56" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -5134,10 +5134,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R56" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="S56" t="inlineStr">
         <is>
@@ -5146,27 +5146,27 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>200056</v>
+        <v>200019</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Evie Thompson</t>
+          <t>Oscar Davies</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Digital Natives</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5176,11 +5176,11 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>East Midlands</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -5189,17 +5189,17 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J57" t="n">
-        <v>25287</v>
+        <v>21651</v>
       </c>
       <c r="K57" t="n">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="L57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -5207,68 +5207,68 @@
         </is>
       </c>
       <c r="N57" t="n">
-        <v>0.17</v>
+        <v>0.8</v>
       </c>
       <c r="O57" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="R57" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>High Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>200057</v>
+        <v>200016</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Amelia Smith</t>
+          <t>Noah Wilson</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Mass Market Mainstream</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>123</v>
+        <v>209</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5277,24 +5277,24 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>948</v>
+        <v>13641</v>
       </c>
       <c r="K58" t="n">
-        <v>142</v>
+        <v>232</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N58" t="n">
-        <v>0.72</v>
+        <v>0.84</v>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -5302,29 +5302,29 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R58" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>200058</v>
+        <v>200028</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sophia Evans</t>
+          <t>Charlie Davies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -5334,25 +5334,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Mass Market Mainstream</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>East Midlands</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5361,10 +5361,10 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>18563</v>
+        <v>11319</v>
       </c>
       <c r="K59" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="N59" t="n">
-        <v>0.43</v>
+        <v>0.61</v>
       </c>
       <c r="O59" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -5386,53 +5386,53 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R59" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>200059</v>
+        <v>200009</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Charlie Evans</t>
+          <t>Freya Brown</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Digital Natives</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>South East</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>145</v>
+        <v>2</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -5445,24 +5445,24 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>19502</v>
+        <v>9130</v>
       </c>
       <c r="K60" t="n">
-        <v>169</v>
+        <v>129</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0.46</v>
+        <v>0.09</v>
       </c>
       <c r="O60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
@@ -5470,10 +5470,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R60" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="S60" t="inlineStr">
         <is>
@@ -5482,32 +5482,32 @@
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>200060</v>
+        <v>200006</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Leo Davies</t>
+          <t>Oscar Jones</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Mass Market Mainstream</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5516,11 +5516,11 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5529,10 +5529,10 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>13960</v>
+        <v>21977</v>
       </c>
       <c r="K61" t="n">
-        <v>12</v>
+        <v>128</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -5543,21 +5543,21 @@
         </is>
       </c>
       <c r="N61" t="n">
-        <v>0.78</v>
+        <v>0.39</v>
       </c>
       <c r="O61" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R61" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -5566,17 +5566,17 @@
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>200061</v>
+        <v>200041</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Emily Patel</t>
+          <t>Thomas Patel</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Comfortable Families</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5596,15 +5596,15 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>East Midlands</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5613,24 +5613,24 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>3788</v>
+        <v>17079</v>
       </c>
       <c r="K62" t="n">
-        <v>224</v>
+        <v>166</v>
       </c>
       <c r="L62" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N62" t="n">
-        <v>0.77</v>
+        <v>0.7</v>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -5638,53 +5638,53 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>200062</v>
+        <v>200014</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Noah White</t>
+          <t>George Williams</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>174</v>
+        <v>338</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -5697,13 +5697,13 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>3131</v>
+        <v>15803</v>
       </c>
       <c r="K63" t="n">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -5711,64 +5711,64 @@
         </is>
       </c>
       <c r="N63" t="n">
-        <v>0.45</v>
+        <v>0.84</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R63" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T63" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>200063</v>
+        <v>200058</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ella Jones</t>
+          <t>Sophia Evans</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Mass Market Mainstream</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>324</v>
+        <v>248</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -5781,10 +5781,10 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>7954</v>
+        <v>18563</v>
       </c>
       <c r="K64" t="n">
-        <v>192</v>
+        <v>38</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -5795,10 +5795,10 @@
         </is>
       </c>
       <c r="N64" t="n">
-        <v>0.65</v>
+        <v>0.43</v>
       </c>
       <c r="O64" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -5806,53 +5806,53 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T64" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>200064</v>
+        <v>200020</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Aarav Patel</t>
+          <t>Evie Davies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Comfortable Families</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>East Midlands</t>
+          <t>Yorkshire</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -5865,10 +5865,10 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>5270</v>
+        <v>2754</v>
       </c>
       <c r="K65" t="n">
-        <v>63</v>
+        <v>226</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -5879,21 +5879,21 @@
         </is>
       </c>
       <c r="N65" t="n">
-        <v>0.67</v>
+        <v>0.37</v>
       </c>
       <c r="O65" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R65" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="S65" t="inlineStr">
         <is>
@@ -5902,17 +5902,17 @@
       </c>
       <c r="T65" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>200065</v>
+        <v>200073</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Emily Taylor</t>
+          <t>Olivia Roberts</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5936,7 +5936,7 @@
         </is>
       </c>
       <c r="G66" t="n">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5949,13 +5949,13 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>22351</v>
+        <v>12384</v>
       </c>
       <c r="K66" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -5963,21 +5963,21 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0.24</v>
+        <v>0.77</v>
       </c>
       <c r="O66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R66" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -5986,17 +5986,17 @@
       </c>
       <c r="T66" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>200066</v>
+        <v>200040</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Freya Evans</t>
+          <t>Amelia Smith</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6011,20 +6011,20 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>155</v>
+        <v>295</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6033,10 +6033,10 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>16333</v>
+        <v>13497</v>
       </c>
       <c r="K67" t="n">
-        <v>28</v>
+        <v>184</v>
       </c>
       <c r="L67" t="n">
         <v>0</v>
@@ -6047,21 +6047,21 @@
         </is>
       </c>
       <c r="N67" t="n">
-        <v>0.49</v>
+        <v>0.71</v>
       </c>
       <c r="O67" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q67" t="n">
         <v>10</v>
       </c>
       <c r="R67" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="S67" t="inlineStr">
         <is>
@@ -6070,27 +6070,27 @@
       </c>
       <c r="T67" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>200067</v>
+        <v>200062</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Aarav Patel</t>
+          <t>Noah White</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6100,15 +6100,15 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>255</v>
+        <v>174</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6117,10 +6117,10 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>25919</v>
+        <v>3131</v>
       </c>
       <c r="K68" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
@@ -6131,10 +6131,10 @@
         </is>
       </c>
       <c r="N68" t="n">
-        <v>0.19</v>
+        <v>0.45</v>
       </c>
       <c r="O68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
@@ -6142,57 +6142,57 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R68" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T68" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>200068</v>
+        <v>200024</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Amelia Patel</t>
+          <t>Mia Williams</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>East Midlands</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>226</v>
+        <v>287</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6201,13 +6201,13 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>4806</v>
+        <v>20837</v>
       </c>
       <c r="K69" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="L69" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -6215,40 +6215,40 @@
         </is>
       </c>
       <c r="N69" t="n">
-        <v>0.35</v>
+        <v>0.73</v>
       </c>
       <c r="O69" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="R69" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>200069</v>
+        <v>200007</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Isla Evans</t>
+          <t>Thomas Wright</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -6263,20 +6263,20 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>152</v>
+        <v>205</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6285,24 +6285,24 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>4273</v>
+        <v>5032</v>
       </c>
       <c r="K70" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="L70" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N70" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="O70" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -6313,54 +6313,54 @@
         <v>10</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T70" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>200070</v>
+        <v>200072</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Jack Smith</t>
+          <t>Jack Thompson</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Over 50</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Comfortable Families</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>East Midlands</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>275</v>
+        <v>344</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6369,13 +6369,13 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>25043</v>
+        <v>18201</v>
       </c>
       <c r="K71" t="n">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="N71" t="n">
-        <v>0.54</v>
+        <v>0.75</v>
       </c>
       <c r="O71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R71" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="S71" t="inlineStr">
         <is>
@@ -6406,17 +6406,17 @@
       </c>
       <c r="T71" t="inlineStr">
         <is>
-          <t>Over 50 Renewal Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>200071</v>
+        <v>200096</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ella Wilson</t>
+          <t>Leo Taylor</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Digital Natives</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6436,15 +6436,15 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G72" t="n">
-        <v>326</v>
+        <v>193</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6453,64 +6453,64 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>10402</v>
+        <v>23203</v>
       </c>
       <c r="K72" t="n">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="L72" t="n">
+        <v>1</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N72" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O72" t="n">
-        <v>4</v>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="R72" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>200072</v>
+        <v>200074</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jack Thompson</t>
+          <t>Harry Jones</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Comfortable Families</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -6520,15 +6520,15 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>East Midlands</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="G73" t="n">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6537,13 +6537,13 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>18201</v>
+        <v>2157</v>
       </c>
       <c r="K73" t="n">
-        <v>108</v>
+        <v>202</v>
       </c>
       <c r="L73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -6551,10 +6551,10 @@
         </is>
       </c>
       <c r="N73" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="O73" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -6562,29 +6562,29 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="R73" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>200073</v>
+        <v>200077</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Olivia Roberts</t>
+          <t>Charlie Thomas</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -6594,40 +6594,40 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="G74" t="n">
-        <v>228</v>
+        <v>330</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J74" t="n">
-        <v>12384</v>
+        <v>16195</v>
       </c>
       <c r="K74" t="n">
-        <v>26</v>
+        <v>217</v>
       </c>
       <c r="L74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -6635,68 +6635,68 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>0.77</v>
+        <v>0.42</v>
       </c>
       <c r="O74" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R74" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>200074</v>
+        <v>200067</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Harry Jones</t>
+          <t>Aarav Patel</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Comfortable Families</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G75" t="n">
-        <v>329</v>
+        <v>255</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6705,10 +6705,10 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>2157</v>
+        <v>25919</v>
       </c>
       <c r="K75" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -6719,40 +6719,40 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>0.67</v>
+        <v>0.19</v>
       </c>
       <c r="O75" t="n">
         <v>3</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R75" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>200075</v>
+        <v>200002</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mia Johnson</t>
+          <t>Mia Thompson</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6762,40 +6762,40 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G76" t="n">
-        <v>306</v>
+        <v>143</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J76" t="n">
-        <v>5241</v>
+        <v>26905</v>
       </c>
       <c r="K76" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -6803,64 +6803,64 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R76" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>200076</v>
+        <v>200022</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Aarav Brown</t>
+          <t>Oscar Patel</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Digital Natives</t>
+          <t>Mass Market Mainstream</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G77" t="n">
-        <v>27</v>
+        <v>325</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -6873,13 +6873,13 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>4224</v>
+        <v>616</v>
       </c>
       <c r="K77" t="n">
-        <v>191</v>
+        <v>86</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -6887,21 +6887,21 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="O77" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="R77" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -6910,17 +6910,17 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>200077</v>
+        <v>200010</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Charlie Thomas</t>
+          <t>Muhammad Roberts</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6930,7 +6930,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -6940,11 +6940,11 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Wales</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G78" t="n">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -6953,82 +6953,82 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J78" t="n">
-        <v>16195</v>
+        <v>518</v>
       </c>
       <c r="K78" t="n">
-        <v>217</v>
+        <v>154</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N78" t="n">
-        <v>0.42</v>
+        <v>0.79</v>
       </c>
       <c r="O78" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R78" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>200078</v>
+        <v>200035</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Noah Taylor</t>
+          <t>Freya Patel</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Mass Market Mainstream</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="G79" t="n">
-        <v>320</v>
+        <v>216</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -7041,13 +7041,13 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>11155</v>
+        <v>23290</v>
       </c>
       <c r="K79" t="n">
-        <v>98</v>
+        <v>6</v>
       </c>
       <c r="L79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -7055,10 +7055,10 @@
         </is>
       </c>
       <c r="N79" t="n">
-        <v>0.39</v>
+        <v>0.32</v>
       </c>
       <c r="O79" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
@@ -7066,53 +7066,53 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R79" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>200079</v>
+        <v>200038</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Freya Thompson</t>
+          <t>Noah White</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>South East</t>
         </is>
       </c>
       <c r="G80" t="n">
-        <v>212</v>
+        <v>277</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -7125,10 +7125,10 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>14131</v>
+        <v>7847</v>
       </c>
       <c r="K80" t="n">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -7139,10 +7139,10 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>0.57</v>
+        <v>0.03</v>
       </c>
       <c r="O80" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
@@ -7150,29 +7150,29 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="R80" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>200080</v>
+        <v>200091</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Noah Jones</t>
+          <t>Sophia Jones</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Comfortable Families</t>
+          <t>Digital Natives</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="G81" t="n">
-        <v>222</v>
+        <v>315</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -7209,13 +7209,13 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>27100</v>
+        <v>19516</v>
       </c>
       <c r="K81" t="n">
-        <v>34</v>
+        <v>142</v>
       </c>
       <c r="L81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -7223,10 +7223,10 @@
         </is>
       </c>
       <c r="N81" t="n">
-        <v>0.48</v>
+        <v>0.03</v>
       </c>
       <c r="O81" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -7234,7 +7234,7 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R81" t="n">
         <v>45</v>
@@ -7246,45 +7246,45 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>200081</v>
+        <v>200046</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Olivia Thomas</t>
+          <t>George Johnson</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Comfortable Families</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>25-34</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G82" t="n">
-        <v>160</v>
+        <v>275</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -7293,24 +7293,24 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>7471</v>
+        <v>6776</v>
       </c>
       <c r="K82" t="n">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="L82" t="n">
         <v>1</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N82" t="n">
-        <v>0.09</v>
+        <v>0.5</v>
       </c>
       <c r="O82" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R82" t="n">
         <v>40</v>
@@ -7330,27 +7330,27 @@
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>200082</v>
+        <v>200078</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Freya Smith</t>
+          <t>Noah Taylor</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7360,15 +7360,15 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G83" t="n">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>6411</v>
+        <v>11155</v>
       </c>
       <c r="K83" t="n">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="L83" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -7391,45 +7391,45 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>200083</v>
+        <v>200029</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Noah Taylor</t>
+          <t>Sophia Taylor</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7439,16 +7439,16 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>65+</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>South East</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="G84" t="n">
-        <v>47</v>
+        <v>216</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -7461,10 +7461,10 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>14257</v>
+        <v>25014</v>
       </c>
       <c r="K84" t="n">
-        <v>117</v>
+        <v>232</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -7475,10 +7475,10 @@
         </is>
       </c>
       <c r="N84" t="n">
-        <v>0.61</v>
+        <v>0.35</v>
       </c>
       <c r="O84" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -7489,54 +7489,54 @@
         <v>8</v>
       </c>
       <c r="R84" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>200084</v>
+        <v>200057</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Isla Patel</t>
+          <t>Amelia Smith</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Mass Market Mainstream</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G85" t="n">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7545,10 +7545,10 @@
         </is>
       </c>
       <c r="J85" t="n">
-        <v>20392</v>
+        <v>948</v>
       </c>
       <c r="K85" t="n">
-        <v>114</v>
+        <v>142</v>
       </c>
       <c r="L85" t="n">
         <v>0</v>
@@ -7559,10 +7559,10 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>0.44</v>
+        <v>0.72</v>
       </c>
       <c r="O85" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R85" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -7582,27 +7582,27 @@
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>200085</v>
+        <v>200063</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Charlie Thomas</t>
+          <t>Ella Jones</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mass Market Mainstream</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -7612,15 +7612,15 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>South East</t>
+          <t>North West</t>
         </is>
       </c>
       <c r="G86" t="n">
-        <v>113</v>
+        <v>324</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7629,24 +7629,24 @@
         </is>
       </c>
       <c r="J86" t="n">
-        <v>751</v>
+        <v>7954</v>
       </c>
       <c r="K86" t="n">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="L86" t="n">
         <v>0</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N86" t="n">
-        <v>0.12</v>
+        <v>0.65</v>
       </c>
       <c r="O86" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="R86" t="n">
         <v>40</v>
@@ -7666,41 +7666,41 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>200086</v>
+        <v>200099</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Isla Taylor</t>
+          <t>Noah Brown</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CTF</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G87" t="n">
-        <v>273</v>
+        <v>231</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -7709,17 +7709,17 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J87" t="n">
-        <v>27807</v>
+        <v>14835</v>
       </c>
       <c r="K87" t="n">
-        <v>172</v>
+        <v>24</v>
       </c>
       <c r="L87" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -7727,10 +7727,10 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0.73</v>
+        <v>0.38</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -7738,39 +7738,39 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="R87" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Medium Priority</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>Send targeted email campaign</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>200087</v>
+        <v>200043</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Thomas Wright</t>
+          <t>Harry Wilson</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Digital Natives</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -7780,15 +7780,15 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="G88" t="n">
-        <v>208</v>
+        <v>292</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7797,24 +7797,24 @@
         </is>
       </c>
       <c r="J88" t="n">
-        <v>4274</v>
+        <v>1440</v>
       </c>
       <c r="K88" t="n">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0.68</v>
+        <v>0.18</v>
       </c>
       <c r="O88" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -7822,10 +7822,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
@@ -7834,17 +7834,17 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>200088</v>
+        <v>200082</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Freya Williams</t>
+          <t>Freya Smith</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -7854,25 +7854,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Comfortable Families</t>
+          <t>Budget Conscious</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>North West</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G89" t="n">
-        <v>224</v>
+        <v>337</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7881,32 +7881,32 @@
         </is>
       </c>
       <c r="J89" t="n">
-        <v>13468</v>
+        <v>6411</v>
       </c>
       <c r="K89" t="n">
-        <v>223</v>
+        <v>70</v>
       </c>
       <c r="L89" t="n">
+        <v>1</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N89" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="O89" t="n">
-        <v>2</v>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R89" t="n">
         <v>35</v>
@@ -7918,27 +7918,27 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>200089</v>
+        <v>200011</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Grace Roberts</t>
+          <t>Noah White</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>CTF</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Budget Conscious</t>
+          <t>Comfortable Families</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -7948,27 +7948,27 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G90" t="n">
-        <v>121</v>
+        <v>273</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J90" t="n">
-        <v>6185</v>
+        <v>16074</v>
       </c>
       <c r="K90" t="n">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -7979,21 +7979,21 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>0.06</v>
+        <v>0.52</v>
       </c>
       <c r="O90" t="n">
+        <v>3</v>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
         <v>12</v>
       </c>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>5</v>
-      </c>
       <c r="R90" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -8002,17 +8002,17 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>200090</v>
+        <v>200068</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Thomas Johnson</t>
+          <t>Amelia Patel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -8022,21 +8022,21 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Mass Market Mainstream</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>East Midlands</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="G91" t="n">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -8049,13 +8049,13 @@
         </is>
       </c>
       <c r="J91" t="n">
-        <v>21189</v>
+        <v>4806</v>
       </c>
       <c r="K91" t="n">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="L91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -8063,83 +8063,83 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O91" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="R91" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>200091</v>
+        <v>200052</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Sophia Jones</t>
+          <t>Amelia Wilson</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>Over 50</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Digital Natives</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G92" t="n">
-        <v>315</v>
+        <v>137</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J92" t="n">
-        <v>19516</v>
+        <v>5936</v>
       </c>
       <c r="K92" t="n">
-        <v>142</v>
+        <v>203</v>
       </c>
       <c r="L92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -8147,10 +8147,10 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>0.03</v>
+        <v>0.48</v>
       </c>
       <c r="O92" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -8158,10 +8158,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="R92" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -8170,17 +8170,17 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>200092</v>
+        <v>200086</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Charlie Taylor</t>
+          <t>Isla Taylor</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -8190,25 +8190,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Mass Market Mainstream</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>South East</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G93" t="n">
-        <v>231</v>
+        <v>273</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -8217,35 +8217,35 @@
         </is>
       </c>
       <c r="J93" t="n">
-        <v>11753</v>
+        <v>27807</v>
       </c>
       <c r="K93" t="n">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="L93" t="n">
+        <v>2</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N93" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O93" t="n">
-        <v>11</v>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R93" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -8254,17 +8254,17 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>CTF Conversion Campaign</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>200093</v>
+        <v>200087</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Grace Roberts</t>
+          <t>Thomas Wright</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8274,25 +8274,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Digital Natives</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>East of England</t>
         </is>
       </c>
       <c r="G94" t="n">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -8301,13 +8301,13 @@
         </is>
       </c>
       <c r="J94" t="n">
-        <v>20091</v>
+        <v>4274</v>
       </c>
       <c r="K94" t="n">
-        <v>14</v>
+        <v>104</v>
       </c>
       <c r="L94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -8315,10 +8315,10 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0.06</v>
+        <v>0.68</v>
       </c>
       <c r="O94" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -8326,39 +8326,39 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R94" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>200094</v>
+        <v>200098</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Leo Jones</t>
+          <t>Charlie Wright</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Cautious Savers</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8368,38 +8368,38 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G95" t="n">
-        <v>340</v>
+        <v>103</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="J95" t="n">
-        <v>21997</v>
+        <v>8692</v>
       </c>
       <c r="K95" t="n">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="L95" t="n">
         <v>1</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N95" t="n">
-        <v>0.6</v>
+        <v>0.47</v>
       </c>
       <c r="O95" t="n">
         <v>1</v>
@@ -8410,53 +8410,53 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R95" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>200095</v>
+        <v>200048</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Charlie Jones</t>
+          <t>Thomas Thomas</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Rising Professionals</t>
+          <t>Affluent Achievers</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>18-24</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Wales</t>
         </is>
       </c>
       <c r="G96" t="n">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -8469,13 +8469,13 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>6406</v>
+        <v>2183</v>
       </c>
       <c r="K96" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -8483,21 +8483,21 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0.16</v>
+        <v>0.7</v>
       </c>
       <c r="O96" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R96" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -8506,27 +8506,27 @@
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>200096</v>
+        <v>200054</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Leo Taylor</t>
+          <t>Thomas Patel</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>JISA</t>
+          <t>ISA</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Affluent Achievers</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8536,11 +8536,11 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>East of England</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G97" t="n">
-        <v>193</v>
+        <v>241</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -8553,54 +8553,54 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>23203</v>
+        <v>9614</v>
       </c>
       <c r="K97" t="n">
-        <v>198</v>
+        <v>47</v>
       </c>
       <c r="L97" t="n">
+        <v>4</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="O97" t="n">
         <v>1</v>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N97" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="O97" t="n">
-        <v>0</v>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R97" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>JISA Maturity Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>200097</v>
+        <v>200069</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ella Thomas</t>
+          <t>Isla Evans</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8610,12 +8610,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Mass Market Mainstream</t>
+          <t>Retired Security Seekers</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>35-44</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8624,37 +8624,37 @@
         </is>
       </c>
       <c r="G98" t="n">
+        <v>152</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>4273</v>
+      </c>
+      <c r="K98" t="n">
         <v>120</v>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>26996</v>
-      </c>
-      <c r="K98" t="n">
-        <v>201</v>
-      </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0.31</v>
+        <v>0.82</v>
       </c>
       <c r="O98" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -8662,53 +8662,53 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="R98" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Medium Priority</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>200098</v>
+        <v>200051</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Charlie Wright</t>
+          <t>Isla Smith</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ISA</t>
+          <t>JISA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Cautious Savers</t>
+          <t>Comfortable Families</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>South West</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="G99" t="n">
-        <v>103</v>
+        <v>231</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -8717,17 +8717,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J99" t="n">
-        <v>8692</v>
+        <v>1569</v>
       </c>
       <c r="K99" t="n">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="L99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M99" t="inlineStr">
         <is>
@@ -8735,7 +8735,7 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>0.47</v>
+        <v>0.73</v>
       </c>
       <c r="O99" t="n">
         <v>1</v>
@@ -8746,10 +8746,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -8758,17 +8758,17 @@
       </c>
       <c r="T99" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>200099</v>
+        <v>200100</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Noah Brown</t>
+          <t>Mia Walker</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -8778,51 +8778,51 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Retired Security Seekers</t>
+          <t>Digital Natives</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>18-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>London</t>
         </is>
       </c>
       <c r="G100" t="n">
-        <v>231</v>
+        <v>192</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J100" t="n">
-        <v>14835</v>
+        <v>3746</v>
       </c>
       <c r="K100" t="n">
-        <v>24</v>
+        <v>215</v>
       </c>
       <c r="L100" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N100" t="n">
-        <v>0.38</v>
+        <v>0.12</v>
       </c>
       <c r="O100" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -8830,10 +8830,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R100" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -8842,17 +8842,17 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>200100</v>
+        <v>200061</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mia Walker</t>
+          <t>Emily Patel</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8862,25 +8862,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Digital Natives</t>
+          <t>Rising Professionals</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>65+</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>South West</t>
         </is>
       </c>
       <c r="G101" t="n">
-        <v>192</v>
+        <v>258</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -8889,21 +8889,21 @@
         </is>
       </c>
       <c r="J101" t="n">
-        <v>3746</v>
+        <v>3788</v>
       </c>
       <c r="K101" t="n">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="L101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="N101" t="n">
-        <v>0.12</v>
+        <v>0.77</v>
       </c>
       <c r="O101" t="n">
         <v>0</v>
@@ -8914,10 +8914,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R101" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S101" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>ISA Retention Call</t>
+          <t>Low priority nurture campaign</t>
         </is>
       </c>
     </row>
